--- a/projectionsv2/rolling_lhb_pf.xlsx
+++ b/projectionsv2/rolling_lhb_pf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dresi\Documents\Baseball Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30B38DE-4C17-451B-957B-614D87AD70DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0697447A-F5EB-4314-A350-672837C3197B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{31A4AC9A-A4C1-4A2B-9B48-AA32E1DA034C}"/>
   </bookViews>
@@ -38,39 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
   <si>
-    <t>Park Factor</t>
-  </si>
-  <si>
-    <t>wOBACon</t>
-  </si>
-  <si>
-    <t>xwOBACon</t>
-  </si>
-  <si>
-    <t>BACON</t>
-  </si>
-  <si>
-    <t>xBACON</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>OBP</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>BB</t>
-  </si>
-  <si>
-    <t>SO</t>
-  </si>
-  <si>
     <t>2022-2024</t>
   </si>
   <si>
@@ -86,15 +53,6 @@
     <t>NYY</t>
   </si>
   <si>
-    <t>X1B</t>
-  </si>
-  <si>
-    <t>X2B</t>
-  </si>
-  <si>
-    <t>X3B</t>
-  </si>
-  <si>
     <t>Season</t>
   </si>
   <si>
@@ -104,9 +62,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>HardHit_pct</t>
-  </si>
-  <si>
     <t>team</t>
   </si>
   <si>
@@ -186,6 +141,51 @@
   </si>
   <si>
     <t>KCR</t>
+  </si>
+  <si>
+    <t>pf</t>
+  </si>
+  <si>
+    <t>wOBAConpf</t>
+  </si>
+  <si>
+    <t>xwOBAConpf</t>
+  </si>
+  <si>
+    <t>BACONpf</t>
+  </si>
+  <si>
+    <t>xBACONpf</t>
+  </si>
+  <si>
+    <t>HardHit_pctpf</t>
+  </si>
+  <si>
+    <t>Rpf</t>
+  </si>
+  <si>
+    <t>OBPpf</t>
+  </si>
+  <si>
+    <t>Hpf</t>
+  </si>
+  <si>
+    <t>X1Bpf</t>
+  </si>
+  <si>
+    <t>X2Bpf</t>
+  </si>
+  <si>
+    <t>X3Bpf</t>
+  </si>
+  <si>
+    <t>HRpf</t>
+  </si>
+  <si>
+    <t>BBpf</t>
+  </si>
+  <si>
+    <t>Sopf</t>
   </si>
 </sst>
 </file>
@@ -2337,69 +2337,69 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="36" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>98</v>
@@ -2449,13 +2449,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D3" s="12">
         <v>101</v>
@@ -2505,13 +2505,13 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D4" s="7">
         <v>97</v>
@@ -2561,13 +2561,13 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3">
         <v>98</v>
@@ -2617,13 +2617,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6">
         <v>99</v>
@@ -2673,13 +2673,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3">
         <v>98</v>
@@ -2729,13 +2729,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>98</v>
@@ -2785,13 +2785,13 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6">
         <v>99</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D10" s="6">
         <v>99</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3">
         <v>98</v>
@@ -2953,13 +2953,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D12" s="8">
         <v>96</v>
@@ -3009,13 +3009,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D13" s="6">
         <v>99</v>
@@ -3065,13 +3065,13 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D14" s="22">
         <v>91</v>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D15" s="13">
         <v>104</v>
@@ -3177,13 +3177,13 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D16" s="8">
         <v>96</v>
@@ -3233,13 +3233,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D17" s="13">
         <v>104</v>
@@ -3289,13 +3289,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5">
         <v>100</v>
@@ -3345,13 +3345,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D19" s="8">
         <v>96</v>
@@ -3401,13 +3401,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D20" s="19">
         <v>103</v>
@@ -3457,13 +3457,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D21" s="13">
         <v>104</v>
@@ -3513,13 +3513,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D22" s="12">
         <v>101</v>
@@ -3569,13 +3569,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D23" s="15">
         <v>94</v>
@@ -3625,13 +3625,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D24" s="10">
         <v>110</v>
@@ -3681,13 +3681,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
         <v>105</v>
@@ -3737,13 +3737,13 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D26" s="10">
         <v>111</v>
@@ -3793,13 +3793,13 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D27" s="19">
         <v>103</v>
@@ -3849,13 +3849,13 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D28" s="7">
         <v>97</v>
@@ -3905,13 +3905,13 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D29" s="4">
         <v>102</v>
@@ -3961,13 +3961,13 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D30" s="6">
         <v>99</v>
@@ -4017,13 +4017,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D31" s="6">
         <v>99</v>

--- a/projectionsv2/rolling_lhb_pf.xlsx
+++ b/projectionsv2/rolling_lhb_pf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dresi\Documents\Baseball Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0697447A-F5EB-4314-A350-672837C3197B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F79E8E6-7CC1-4D23-B99A-981FC0314A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{31A4AC9A-A4C1-4A2B-9B48-AA32E1DA034C}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{31A4AC9A-A4C1-4A2B-9B48-AA32E1DA034C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="46">
   <si>
     <t>2022-2024</t>
   </si>
@@ -144,18 +144,6 @@
   </si>
   <si>
     <t>pf</t>
-  </si>
-  <si>
-    <t>wOBAConpf</t>
-  </si>
-  <si>
-    <t>xwOBAConpf</t>
-  </si>
-  <si>
-    <t>BACONpf</t>
-  </si>
-  <si>
-    <t>xBACONpf</t>
   </si>
   <si>
     <t>HardHit_pctpf</t>
@@ -2332,10 +2320,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC33B641-6DEF-4FE1-BA82-C9A6237F8BFA}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="36" t="s">
         <v>8</v>
       </c>
@@ -2378,20 +2366,8 @@
       <c r="N1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>49</v>
-      </c>
     </row>
-    <row r="2" spans="1:18" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2404,50 +2380,38 @@
       <c r="D2" s="3">
         <v>98</v>
       </c>
-      <c r="E2" s="4">
-        <v>102</v>
-      </c>
-      <c r="F2" s="5">
-        <v>100</v>
-      </c>
-      <c r="G2" s="6">
-        <v>99</v>
-      </c>
-      <c r="H2" s="6">
-        <v>99</v>
-      </c>
-      <c r="I2" s="7">
+      <c r="E2" s="7">
         <v>97</v>
       </c>
-      <c r="J2" s="8">
+      <c r="F2" s="8">
         <v>96</v>
       </c>
-      <c r="K2" s="7">
+      <c r="G2" s="7">
         <v>97</v>
       </c>
-      <c r="L2" s="7">
+      <c r="H2" s="7">
         <v>97</v>
       </c>
-      <c r="M2" s="8">
+      <c r="I2" s="8">
         <v>96</v>
       </c>
-      <c r="N2" s="9">
+      <c r="J2" s="9">
         <v>82</v>
       </c>
-      <c r="O2" s="10">
+      <c r="K2" s="10">
         <v>117</v>
       </c>
-      <c r="P2" s="10">
+      <c r="L2" s="10">
         <v>118</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="M2" s="7">
         <v>97</v>
       </c>
-      <c r="R2" s="10">
+      <c r="N2" s="10">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2460,50 +2424,38 @@
       <c r="D3" s="12">
         <v>101</v>
       </c>
-      <c r="E3" s="4">
-        <v>102</v>
+      <c r="E3" s="12">
+        <v>101</v>
       </c>
       <c r="F3" s="4">
         <v>102</v>
       </c>
-      <c r="G3" s="12">
-        <v>101</v>
-      </c>
-      <c r="H3" s="12">
-        <v>101</v>
-      </c>
-      <c r="I3" s="12">
-        <v>101</v>
-      </c>
-      <c r="J3" s="4">
-        <v>102</v>
-      </c>
-      <c r="K3" s="5">
+      <c r="G3" s="5">
         <v>100</v>
       </c>
-      <c r="L3" s="6">
+      <c r="H3" s="6">
         <v>99</v>
       </c>
-      <c r="M3" s="7">
+      <c r="I3" s="7">
         <v>97</v>
       </c>
-      <c r="N3" s="3">
+      <c r="J3" s="3">
         <v>98</v>
       </c>
-      <c r="O3" s="10">
+      <c r="K3" s="10">
         <v>115</v>
       </c>
-      <c r="P3" s="10">
+      <c r="L3" s="10">
         <v>110</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="M3" s="13">
         <v>104</v>
       </c>
-      <c r="R3" s="14">
+      <c r="N3" s="14">
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2516,50 +2468,38 @@
       <c r="D4" s="7">
         <v>97</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="17">
+        <v>93</v>
+      </c>
+      <c r="F4" s="15">
         <v>94</v>
       </c>
-      <c r="F4" s="8">
-        <v>96</v>
-      </c>
-      <c r="G4" s="16">
+      <c r="G4" s="3">
+        <v>98</v>
+      </c>
+      <c r="H4" s="16">
         <v>95</v>
       </c>
-      <c r="H4" s="8">
-        <v>96</v>
-      </c>
-      <c r="I4" s="17">
-        <v>93</v>
-      </c>
-      <c r="J4" s="15">
+      <c r="I4" s="15">
         <v>94</v>
       </c>
-      <c r="K4" s="3">
-        <v>98</v>
-      </c>
-      <c r="L4" s="16">
+      <c r="J4" s="18">
+        <v>106</v>
+      </c>
+      <c r="K4" s="10">
+        <v>115</v>
+      </c>
+      <c r="L4" s="9">
+        <v>81</v>
+      </c>
+      <c r="M4" s="19">
+        <v>103</v>
+      </c>
+      <c r="N4" s="16">
         <v>95</v>
       </c>
-      <c r="M4" s="15">
-        <v>94</v>
-      </c>
-      <c r="N4" s="18">
-        <v>106</v>
-      </c>
-      <c r="O4" s="10">
-        <v>115</v>
-      </c>
-      <c r="P4" s="9">
-        <v>81</v>
-      </c>
-      <c r="Q4" s="19">
-        <v>103</v>
-      </c>
-      <c r="R4" s="16">
-        <v>95</v>
-      </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2572,50 +2512,38 @@
       <c r="D5" s="3">
         <v>98</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
+        <v>98</v>
+      </c>
+      <c r="F5" s="8">
+        <v>96</v>
+      </c>
+      <c r="G5" s="6">
         <v>99</v>
       </c>
-      <c r="F5" s="3">
-        <v>98</v>
-      </c>
-      <c r="G5" s="3">
-        <v>98</v>
-      </c>
-      <c r="H5" s="6">
-        <v>99</v>
-      </c>
-      <c r="I5" s="3">
-        <v>98</v>
-      </c>
-      <c r="J5" s="8">
-        <v>96</v>
-      </c>
-      <c r="K5" s="6">
-        <v>99</v>
-      </c>
-      <c r="L5" s="7">
+      <c r="H5" s="7">
         <v>97</v>
       </c>
-      <c r="M5" s="17">
+      <c r="I5" s="17">
         <v>93</v>
       </c>
-      <c r="N5" s="10">
+      <c r="J5" s="10">
         <v>114</v>
       </c>
-      <c r="O5" s="17">
+      <c r="K5" s="17">
         <v>93</v>
       </c>
-      <c r="P5" s="16">
+      <c r="L5" s="16">
         <v>95</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="M5" s="19">
         <v>103</v>
       </c>
-      <c r="R5" s="13">
+      <c r="N5" s="13">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2628,50 +2556,38 @@
       <c r="D6" s="6">
         <v>99</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="4">
+        <v>102</v>
+      </c>
+      <c r="F6" s="3">
+        <v>98</v>
+      </c>
+      <c r="G6" s="6">
+        <v>99</v>
+      </c>
+      <c r="H6" s="12">
+        <v>101</v>
+      </c>
+      <c r="I6" s="14">
         <v>105</v>
       </c>
-      <c r="F6" s="19">
-        <v>103</v>
-      </c>
-      <c r="G6" s="14">
-        <v>105</v>
-      </c>
-      <c r="H6" s="19">
-        <v>103</v>
-      </c>
-      <c r="I6" s="4">
-        <v>102</v>
-      </c>
-      <c r="J6" s="3">
-        <v>98</v>
-      </c>
-      <c r="K6" s="6">
-        <v>99</v>
-      </c>
-      <c r="L6" s="12">
-        <v>101</v>
-      </c>
-      <c r="M6" s="14">
-        <v>105</v>
-      </c>
-      <c r="N6" s="9">
+      <c r="J6" s="9">
         <v>90</v>
       </c>
-      <c r="O6" s="15">
+      <c r="K6" s="15">
         <v>94</v>
       </c>
-      <c r="P6" s="13">
+      <c r="L6" s="13">
         <v>104</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="M6" s="20">
         <v>92</v>
       </c>
-      <c r="R6" s="10">
+      <c r="N6" s="10">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2684,50 +2600,38 @@
       <c r="D7" s="3">
         <v>98</v>
       </c>
-      <c r="E7" s="5">
-        <v>100</v>
-      </c>
-      <c r="F7" s="5">
-        <v>100</v>
+      <c r="E7" s="3">
+        <v>98</v>
+      </c>
+      <c r="F7" s="8">
+        <v>96</v>
       </c>
       <c r="G7" s="7">
         <v>97</v>
       </c>
-      <c r="H7" s="5">
-        <v>100</v>
-      </c>
-      <c r="I7" s="3">
-        <v>98</v>
-      </c>
-      <c r="J7" s="8">
-        <v>96</v>
-      </c>
-      <c r="K7" s="7">
-        <v>97</v>
-      </c>
-      <c r="L7" s="17">
+      <c r="H7" s="17">
         <v>93</v>
       </c>
-      <c r="M7" s="9">
+      <c r="I7" s="9">
         <v>90</v>
       </c>
-      <c r="N7" s="9">
+      <c r="J7" s="9">
         <v>84</v>
       </c>
-      <c r="O7" s="21">
+      <c r="K7" s="21">
         <v>108</v>
       </c>
-      <c r="P7" s="10">
+      <c r="L7" s="10">
         <v>119</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="M7" s="21">
         <v>108</v>
       </c>
-      <c r="R7" s="10">
+      <c r="N7" s="10">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2740,50 +2644,38 @@
       <c r="D8" s="3">
         <v>98</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
+        <v>99</v>
+      </c>
+      <c r="F8" s="8">
         <v>96</v>
       </c>
-      <c r="F8" s="5">
-        <v>100</v>
-      </c>
-      <c r="G8" s="7">
-        <v>97</v>
+      <c r="G8" s="6">
+        <v>99</v>
       </c>
       <c r="H8" s="5">
         <v>100</v>
       </c>
-      <c r="I8" s="6">
-        <v>99</v>
-      </c>
-      <c r="J8" s="8">
+      <c r="I8" s="13">
+        <v>104</v>
+      </c>
+      <c r="J8" s="5">
+        <v>100</v>
+      </c>
+      <c r="K8" s="8">
         <v>96</v>
       </c>
-      <c r="K8" s="6">
-        <v>99</v>
-      </c>
-      <c r="L8" s="5">
-        <v>100</v>
-      </c>
-      <c r="M8" s="13">
-        <v>104</v>
-      </c>
-      <c r="N8" s="5">
-        <v>100</v>
-      </c>
-      <c r="O8" s="8">
-        <v>96</v>
-      </c>
-      <c r="P8" s="9">
+      <c r="L8" s="9">
         <v>87</v>
       </c>
-      <c r="Q8" s="15">
+      <c r="M8" s="15">
         <v>94</v>
       </c>
-      <c r="R8" s="22">
+      <c r="N8" s="22">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2796,50 +2688,38 @@
       <c r="D9" s="6">
         <v>99</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="5">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>98</v>
+      </c>
+      <c r="G9" s="5">
+        <v>100</v>
+      </c>
+      <c r="H9" s="12">
         <v>101</v>
       </c>
-      <c r="F9" s="5">
-        <v>100</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="I9" s="4">
         <v>102</v>
       </c>
-      <c r="H9" s="5">
-        <v>100</v>
-      </c>
-      <c r="I9" s="5">
-        <v>100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>98</v>
-      </c>
-      <c r="K9" s="5">
-        <v>100</v>
-      </c>
-      <c r="L9" s="12">
-        <v>101</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="J9" s="4">
         <v>102</v>
       </c>
-      <c r="N9" s="4">
-        <v>102</v>
-      </c>
-      <c r="O9" s="10">
+      <c r="K9" s="10">
         <v>130</v>
       </c>
-      <c r="P9" s="9">
+      <c r="L9" s="9">
         <v>90</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="M9" s="19">
         <v>103</v>
       </c>
-      <c r="R9" s="18">
+      <c r="N9" s="18">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2852,50 +2732,38 @@
       <c r="D10" s="6">
         <v>99</v>
       </c>
-      <c r="E10" s="7">
-        <v>97</v>
-      </c>
-      <c r="F10" s="16">
-        <v>95</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="E10" s="3">
         <v>98</v>
       </c>
-      <c r="H10" s="7">
-        <v>97</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="F10" s="3">
         <v>98</v>
       </c>
-      <c r="J10" s="3">
-        <v>98</v>
-      </c>
-      <c r="K10" s="5">
+      <c r="G10" s="5">
         <v>100</v>
       </c>
-      <c r="L10" s="12">
+      <c r="H10" s="12">
         <v>101</v>
+      </c>
+      <c r="I10" s="4">
+        <v>102</v>
+      </c>
+      <c r="J10" s="18">
+        <v>106</v>
+      </c>
+      <c r="K10" s="10">
+        <v>177</v>
+      </c>
+      <c r="L10" s="23">
+        <v>76</v>
       </c>
       <c r="M10" s="4">
         <v>102</v>
       </c>
-      <c r="N10" s="18">
-        <v>106</v>
-      </c>
-      <c r="O10" s="10">
-        <v>177</v>
-      </c>
-      <c r="P10" s="23">
-        <v>76</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>102</v>
-      </c>
-      <c r="R10" s="15">
+      <c r="N10" s="15">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2908,50 +2776,38 @@
       <c r="D11" s="3">
         <v>98</v>
       </c>
-      <c r="E11" s="3">
-        <v>98</v>
-      </c>
-      <c r="F11" s="12">
-        <v>101</v>
+      <c r="E11" s="4">
+        <v>102</v>
+      </c>
+      <c r="F11" s="8">
+        <v>96</v>
       </c>
       <c r="G11" s="8">
         <v>96</v>
       </c>
-      <c r="H11" s="5">
-        <v>100</v>
-      </c>
-      <c r="I11" s="4">
-        <v>102</v>
-      </c>
-      <c r="J11" s="8">
-        <v>96</v>
-      </c>
-      <c r="K11" s="8">
-        <v>96</v>
-      </c>
-      <c r="L11" s="16">
+      <c r="H11" s="16">
         <v>95</v>
       </c>
-      <c r="M11" s="20">
+      <c r="I11" s="20">
         <v>92</v>
       </c>
-      <c r="N11" s="16">
+      <c r="J11" s="16">
         <v>95</v>
       </c>
-      <c r="O11" s="23">
+      <c r="K11" s="23">
         <v>76</v>
       </c>
-      <c r="P11" s="10">
+      <c r="L11" s="10">
         <v>116</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="M11" s="17">
         <v>93</v>
       </c>
-      <c r="R11" s="12">
+      <c r="N11" s="12">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2964,50 +2820,38 @@
       <c r="D12" s="8">
         <v>96</v>
       </c>
-      <c r="E12" s="8">
-        <v>96</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="14">
+        <v>105</v>
+      </c>
+      <c r="F12" s="20">
+        <v>92</v>
+      </c>
+      <c r="G12" s="7">
+        <v>97</v>
+      </c>
+      <c r="H12" s="5">
+        <v>100</v>
+      </c>
+      <c r="I12" s="13">
+        <v>104</v>
+      </c>
+      <c r="J12" s="4">
+        <v>102</v>
+      </c>
+      <c r="K12" s="10">
+        <v>113</v>
+      </c>
+      <c r="L12" s="24">
+        <v>77</v>
+      </c>
+      <c r="M12" s="15">
+        <v>94</v>
+      </c>
+      <c r="N12" s="6">
         <v>99</v>
       </c>
-      <c r="G12" s="6">
-        <v>99</v>
-      </c>
-      <c r="H12" s="6">
-        <v>99</v>
-      </c>
-      <c r="I12" s="14">
-        <v>105</v>
-      </c>
-      <c r="J12" s="20">
-        <v>92</v>
-      </c>
-      <c r="K12" s="7">
-        <v>97</v>
-      </c>
-      <c r="L12" s="5">
-        <v>100</v>
-      </c>
-      <c r="M12" s="13">
-        <v>104</v>
-      </c>
-      <c r="N12" s="4">
-        <v>102</v>
-      </c>
-      <c r="O12" s="10">
-        <v>113</v>
-      </c>
-      <c r="P12" s="24">
-        <v>77</v>
-      </c>
-      <c r="Q12" s="15">
-        <v>94</v>
-      </c>
-      <c r="R12" s="6">
-        <v>99</v>
-      </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3020,50 +2864,38 @@
       <c r="D13" s="6">
         <v>99</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="8">
+        <v>96</v>
+      </c>
+      <c r="F13" s="3">
         <v>98</v>
       </c>
-      <c r="F13" s="7">
-        <v>97</v>
-      </c>
-      <c r="G13" s="6">
-        <v>99</v>
-      </c>
-      <c r="H13" s="6">
-        <v>99</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="G13" s="5">
+        <v>100</v>
+      </c>
+      <c r="H13" s="4">
+        <v>102</v>
+      </c>
+      <c r="I13" s="13">
+        <v>104</v>
+      </c>
+      <c r="J13" s="14">
+        <v>105</v>
+      </c>
+      <c r="K13" s="25">
+        <v>46</v>
+      </c>
+      <c r="L13" s="8">
         <v>96</v>
       </c>
-      <c r="J13" s="3">
-        <v>98</v>
-      </c>
-      <c r="K13" s="5">
-        <v>100</v>
-      </c>
-      <c r="L13" s="4">
-        <v>102</v>
-      </c>
-      <c r="M13" s="13">
-        <v>104</v>
-      </c>
-      <c r="N13" s="14">
-        <v>105</v>
-      </c>
-      <c r="O13" s="25">
-        <v>46</v>
-      </c>
-      <c r="P13" s="8">
-        <v>96</v>
-      </c>
-      <c r="Q13" s="17">
+      <c r="M13" s="17">
         <v>93</v>
       </c>
-      <c r="R13" s="17">
+      <c r="N13" s="17">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3076,50 +2908,38 @@
       <c r="D14" s="22">
         <v>91</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="7">
+        <v>97</v>
+      </c>
+      <c r="F14" s="9">
+        <v>83</v>
+      </c>
+      <c r="G14" s="22">
+        <v>91</v>
+      </c>
+      <c r="H14" s="22">
+        <v>91</v>
+      </c>
+      <c r="I14" s="15">
         <v>94</v>
       </c>
-      <c r="F14" s="3">
-        <v>98</v>
-      </c>
-      <c r="G14" s="16">
-        <v>95</v>
-      </c>
-      <c r="H14" s="6">
-        <v>99</v>
-      </c>
-      <c r="I14" s="7">
-        <v>97</v>
-      </c>
       <c r="J14" s="9">
-        <v>83</v>
-      </c>
-      <c r="K14" s="22">
-        <v>91</v>
-      </c>
-      <c r="L14" s="22">
-        <v>91</v>
-      </c>
-      <c r="M14" s="15">
-        <v>94</v>
-      </c>
-      <c r="N14" s="9">
         <v>86</v>
       </c>
-      <c r="O14" s="26">
+      <c r="K14" s="26">
         <v>52</v>
       </c>
-      <c r="P14" s="20">
+      <c r="L14" s="20">
         <v>92</v>
       </c>
-      <c r="Q14" s="20">
+      <c r="M14" s="20">
         <v>92</v>
       </c>
-      <c r="R14" s="10">
+      <c r="N14" s="10">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3132,50 +2952,38 @@
       <c r="D15" s="13">
         <v>104</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="7">
+        <v>97</v>
+      </c>
+      <c r="F15" s="21">
+        <v>108</v>
+      </c>
+      <c r="G15" s="13">
+        <v>104</v>
+      </c>
+      <c r="H15" s="27">
+        <v>107</v>
+      </c>
+      <c r="I15" s="14">
         <v>105</v>
       </c>
-      <c r="F15" s="19">
-        <v>103</v>
-      </c>
-      <c r="G15" s="14">
-        <v>105</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="J15" s="10">
+        <v>112</v>
+      </c>
+      <c r="K15" s="10">
+        <v>129</v>
+      </c>
+      <c r="L15" s="4">
         <v>102</v>
       </c>
-      <c r="I15" s="7">
-        <v>97</v>
-      </c>
-      <c r="J15" s="21">
-        <v>108</v>
-      </c>
-      <c r="K15" s="13">
-        <v>104</v>
-      </c>
-      <c r="L15" s="27">
-        <v>107</v>
-      </c>
-      <c r="M15" s="14">
-        <v>105</v>
-      </c>
-      <c r="N15" s="10">
-        <v>112</v>
-      </c>
-      <c r="O15" s="10">
-        <v>129</v>
-      </c>
-      <c r="P15" s="4">
-        <v>102</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="M15" s="3">
         <v>98</v>
       </c>
-      <c r="R15" s="3">
+      <c r="N15" s="3">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3188,50 +2996,38 @@
       <c r="D16" s="8">
         <v>96</v>
       </c>
-      <c r="E16" s="16">
-        <v>95</v>
-      </c>
-      <c r="F16" s="8">
-        <v>96</v>
-      </c>
-      <c r="G16" s="16">
-        <v>95</v>
-      </c>
-      <c r="H16" s="8">
-        <v>96</v>
-      </c>
-      <c r="I16" s="7">
+      <c r="E16" s="7">
         <v>97</v>
       </c>
-      <c r="J16" s="20">
+      <c r="F16" s="20">
         <v>92</v>
       </c>
-      <c r="K16" s="3">
+      <c r="G16" s="3">
         <v>98</v>
       </c>
-      <c r="L16" s="22">
+      <c r="H16" s="22">
         <v>91</v>
       </c>
-      <c r="M16" s="15">
+      <c r="I16" s="15">
         <v>94</v>
       </c>
-      <c r="N16" s="9">
+      <c r="J16" s="9">
         <v>86</v>
       </c>
-      <c r="O16" s="28">
+      <c r="K16" s="28">
         <v>65</v>
       </c>
-      <c r="P16" s="17">
+      <c r="L16" s="17">
         <v>93</v>
       </c>
-      <c r="Q16" s="29">
+      <c r="M16" s="29">
         <v>109</v>
       </c>
-      <c r="R16" s="14">
+      <c r="N16" s="14">
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3247,47 +3043,35 @@
       <c r="E17" s="5">
         <v>100</v>
       </c>
-      <c r="F17" s="12">
-        <v>101</v>
-      </c>
-      <c r="G17" s="12">
-        <v>101</v>
-      </c>
-      <c r="H17" s="12">
-        <v>101</v>
-      </c>
-      <c r="I17" s="5">
+      <c r="F17" s="21">
+        <v>108</v>
+      </c>
+      <c r="G17" s="13">
+        <v>104</v>
+      </c>
+      <c r="H17" s="21">
+        <v>108</v>
+      </c>
+      <c r="I17" s="10">
+        <v>112</v>
+      </c>
+      <c r="J17" s="19">
+        <v>103</v>
+      </c>
+      <c r="K17" s="30">
+        <v>75</v>
+      </c>
+      <c r="L17" s="5">
         <v>100</v>
       </c>
-      <c r="J17" s="21">
-        <v>108</v>
-      </c>
-      <c r="K17" s="13">
-        <v>104</v>
-      </c>
-      <c r="L17" s="21">
-        <v>108</v>
-      </c>
-      <c r="M17" s="10">
-        <v>112</v>
-      </c>
-      <c r="N17" s="19">
-        <v>103</v>
-      </c>
-      <c r="O17" s="30">
-        <v>75</v>
-      </c>
-      <c r="P17" s="5">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="15">
+      <c r="M17" s="15">
         <v>94</v>
       </c>
-      <c r="R17" s="9">
+      <c r="N17" s="9">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3300,50 +3084,38 @@
       <c r="D18" s="5">
         <v>100</v>
       </c>
-      <c r="E18" s="5">
-        <v>100</v>
+      <c r="E18" s="13">
+        <v>104</v>
       </c>
       <c r="F18" s="5">
         <v>100</v>
       </c>
-      <c r="G18" s="5">
-        <v>100</v>
-      </c>
-      <c r="H18" s="5">
-        <v>100</v>
-      </c>
-      <c r="I18" s="13">
-        <v>104</v>
-      </c>
-      <c r="J18" s="5">
-        <v>100</v>
-      </c>
-      <c r="K18" s="6">
+      <c r="G18" s="6">
         <v>99</v>
       </c>
-      <c r="L18" s="19">
+      <c r="H18" s="19">
         <v>103</v>
       </c>
-      <c r="M18" s="27">
+      <c r="I18" s="27">
         <v>107</v>
       </c>
-      <c r="N18" s="9">
+      <c r="J18" s="9">
         <v>88</v>
       </c>
-      <c r="O18" s="24">
+      <c r="K18" s="24">
         <v>77</v>
       </c>
-      <c r="P18" s="10">
+      <c r="L18" s="10">
         <v>111</v>
       </c>
-      <c r="Q18" s="22">
+      <c r="M18" s="22">
         <v>91</v>
       </c>
-      <c r="R18" s="15">
+      <c r="N18" s="15">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3356,50 +3128,38 @@
       <c r="D19" s="8">
         <v>96</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="12">
+        <v>101</v>
+      </c>
+      <c r="F19" s="20">
+        <v>92</v>
+      </c>
+      <c r="G19" s="7">
+        <v>97</v>
+      </c>
+      <c r="H19" s="15">
         <v>94</v>
       </c>
-      <c r="F19" s="6">
-        <v>99</v>
-      </c>
-      <c r="G19" s="16">
-        <v>95</v>
-      </c>
-      <c r="H19" s="6">
-        <v>99</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="I19" s="8">
+        <v>96</v>
+      </c>
+      <c r="J19" s="7">
+        <v>97</v>
+      </c>
+      <c r="K19" s="31">
+        <v>42</v>
+      </c>
+      <c r="L19" s="17">
+        <v>93</v>
+      </c>
+      <c r="M19" s="12">
         <v>101</v>
       </c>
-      <c r="J19" s="20">
-        <v>92</v>
-      </c>
-      <c r="K19" s="7">
-        <v>97</v>
-      </c>
-      <c r="L19" s="15">
-        <v>94</v>
-      </c>
-      <c r="M19" s="8">
-        <v>96</v>
-      </c>
-      <c r="N19" s="7">
-        <v>97</v>
-      </c>
-      <c r="O19" s="31">
-        <v>42</v>
-      </c>
-      <c r="P19" s="17">
-        <v>93</v>
-      </c>
-      <c r="Q19" s="12">
-        <v>101</v>
-      </c>
-      <c r="R19" s="5">
+      <c r="N19" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3412,50 +3172,38 @@
       <c r="D20" s="19">
         <v>103</v>
       </c>
-      <c r="E20" s="14">
-        <v>105</v>
-      </c>
-      <c r="F20" s="19">
-        <v>103</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="E20" s="4">
         <v>102</v>
+      </c>
+      <c r="F20" s="18">
+        <v>106</v>
+      </c>
+      <c r="G20" s="12">
+        <v>101</v>
       </c>
       <c r="H20" s="12">
         <v>101</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="7">
+        <v>97</v>
+      </c>
+      <c r="J20" s="20">
+        <v>92</v>
+      </c>
+      <c r="K20" s="10">
+        <v>125</v>
+      </c>
+      <c r="L20" s="10">
+        <v>127</v>
+      </c>
+      <c r="M20" s="4">
         <v>102</v>
       </c>
-      <c r="J20" s="18">
-        <v>106</v>
-      </c>
-      <c r="K20" s="12">
-        <v>101</v>
-      </c>
-      <c r="L20" s="12">
-        <v>101</v>
-      </c>
-      <c r="M20" s="7">
-        <v>97</v>
-      </c>
-      <c r="N20" s="20">
-        <v>92</v>
-      </c>
-      <c r="O20" s="10">
-        <v>125</v>
-      </c>
-      <c r="P20" s="10">
-        <v>127</v>
-      </c>
-      <c r="Q20" s="4">
+      <c r="N20" s="4">
         <v>102</v>
       </c>
-      <c r="R20" s="4">
-        <v>102</v>
-      </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3468,50 +3216,38 @@
       <c r="D21" s="13">
         <v>104</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="13">
+        <v>104</v>
+      </c>
+      <c r="F21" s="21">
+        <v>108</v>
+      </c>
+      <c r="G21" s="14">
+        <v>105</v>
+      </c>
+      <c r="H21" s="13">
+        <v>104</v>
+      </c>
+      <c r="I21" s="19">
+        <v>103</v>
+      </c>
+      <c r="J21" s="10">
+        <v>113</v>
+      </c>
+      <c r="K21" s="32">
+        <v>68</v>
+      </c>
+      <c r="L21" s="4">
         <v>102</v>
       </c>
-      <c r="F21" s="19">
-        <v>103</v>
-      </c>
-      <c r="G21" s="19">
-        <v>103</v>
-      </c>
-      <c r="H21" s="12">
-        <v>101</v>
-      </c>
-      <c r="I21" s="13">
-        <v>104</v>
-      </c>
-      <c r="J21" s="21">
-        <v>108</v>
-      </c>
-      <c r="K21" s="14">
+      <c r="M21" s="14">
         <v>105</v>
       </c>
-      <c r="L21" s="13">
-        <v>104</v>
-      </c>
-      <c r="M21" s="19">
-        <v>103</v>
-      </c>
-      <c r="N21" s="10">
-        <v>113</v>
-      </c>
-      <c r="O21" s="32">
-        <v>68</v>
-      </c>
-      <c r="P21" s="4">
-        <v>102</v>
-      </c>
-      <c r="Q21" s="14">
-        <v>105</v>
-      </c>
-      <c r="R21" s="17">
+      <c r="N21" s="17">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3524,50 +3260,38 @@
       <c r="D22" s="12">
         <v>101</v>
       </c>
-      <c r="E22" s="12">
-        <v>101</v>
+      <c r="E22" s="14">
+        <v>105</v>
       </c>
       <c r="F22" s="4">
         <v>102</v>
       </c>
-      <c r="G22" s="6">
-        <v>99</v>
-      </c>
-      <c r="H22" s="12">
+      <c r="G22" s="5">
+        <v>100</v>
+      </c>
+      <c r="H22" s="4">
+        <v>102</v>
+      </c>
+      <c r="I22" s="5">
+        <v>100</v>
+      </c>
+      <c r="J22" s="12">
         <v>101</v>
       </c>
-      <c r="I22" s="14">
-        <v>105</v>
-      </c>
-      <c r="J22" s="4">
+      <c r="K22" s="33">
+        <v>67</v>
+      </c>
+      <c r="L22" s="10">
+        <v>113</v>
+      </c>
+      <c r="M22" s="4">
         <v>102</v>
       </c>
-      <c r="K22" s="5">
-        <v>100</v>
-      </c>
-      <c r="L22" s="4">
-        <v>102</v>
-      </c>
-      <c r="M22" s="5">
-        <v>100</v>
-      </c>
-      <c r="N22" s="12">
-        <v>101</v>
-      </c>
-      <c r="O22" s="33">
-        <v>67</v>
-      </c>
-      <c r="P22" s="10">
-        <v>113</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>102</v>
-      </c>
-      <c r="R22" s="7">
+      <c r="N22" s="7">
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3580,50 +3304,38 @@
       <c r="D23" s="15">
         <v>94</v>
       </c>
-      <c r="E23" s="3">
-        <v>98</v>
-      </c>
-      <c r="F23" s="3">
-        <v>98</v>
-      </c>
-      <c r="G23" s="6">
-        <v>99</v>
-      </c>
-      <c r="H23" s="6">
-        <v>99</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="E23" s="8">
         <v>96</v>
       </c>
-      <c r="J23" s="9">
+      <c r="F23" s="9">
         <v>88</v>
       </c>
-      <c r="K23" s="15">
+      <c r="G23" s="15">
         <v>94</v>
       </c>
-      <c r="L23" s="15">
+      <c r="H23" s="15">
         <v>94</v>
+      </c>
+      <c r="I23" s="15">
+        <v>94</v>
+      </c>
+      <c r="J23" s="8">
+        <v>96</v>
+      </c>
+      <c r="K23" s="19">
+        <v>103</v>
+      </c>
+      <c r="L23" s="9">
+        <v>88</v>
       </c>
       <c r="M23" s="15">
         <v>94</v>
       </c>
-      <c r="N23" s="8">
-        <v>96</v>
-      </c>
-      <c r="O23" s="19">
-        <v>103</v>
-      </c>
-      <c r="P23" s="9">
-        <v>88</v>
-      </c>
-      <c r="Q23" s="15">
-        <v>94</v>
-      </c>
-      <c r="R23" s="10">
+      <c r="N23" s="10">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3636,50 +3348,38 @@
       <c r="D24" s="10">
         <v>110</v>
       </c>
-      <c r="E24" s="21">
-        <v>108</v>
-      </c>
-      <c r="F24" s="19">
-        <v>103</v>
-      </c>
-      <c r="G24" s="21">
-        <v>108</v>
-      </c>
-      <c r="H24" s="19">
-        <v>103</v>
-      </c>
-      <c r="I24" s="13">
+      <c r="E24" s="13">
         <v>104</v>
       </c>
+      <c r="F24" s="10">
+        <v>121</v>
+      </c>
+      <c r="G24" s="29">
+        <v>109</v>
+      </c>
+      <c r="H24" s="10">
+        <v>113</v>
+      </c>
+      <c r="I24" s="27">
+        <v>107</v>
+      </c>
       <c r="J24" s="10">
-        <v>121</v>
-      </c>
-      <c r="K24" s="29">
-        <v>109</v>
-      </c>
-      <c r="L24" s="10">
-        <v>113</v>
-      </c>
-      <c r="M24" s="27">
-        <v>107</v>
-      </c>
-      <c r="N24" s="10">
         <v>142</v>
       </c>
-      <c r="O24" s="10">
+      <c r="K24" s="10">
         <v>120</v>
       </c>
-      <c r="P24" s="8">
+      <c r="L24" s="8">
         <v>96</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="M24" s="6">
         <v>99</v>
       </c>
-      <c r="R24" s="9">
+      <c r="N24" s="9">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3692,50 +3392,38 @@
       <c r="D25" s="14">
         <v>105</v>
       </c>
-      <c r="E25" s="21">
-        <v>108</v>
-      </c>
-      <c r="F25" s="3">
-        <v>98</v>
-      </c>
-      <c r="G25" s="19">
-        <v>103</v>
-      </c>
-      <c r="H25" s="3">
-        <v>98</v>
+      <c r="E25" s="15">
+        <v>94</v>
+      </c>
+      <c r="F25" s="10">
+        <v>110</v>
+      </c>
+      <c r="G25" s="4">
+        <v>102</v>
+      </c>
+      <c r="H25" s="12">
+        <v>101</v>
       </c>
       <c r="I25" s="15">
         <v>94</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="8">
+        <v>96</v>
+      </c>
+      <c r="K25" s="10">
         <v>110</v>
       </c>
-      <c r="K25" s="4">
-        <v>102</v>
-      </c>
-      <c r="L25" s="12">
-        <v>101</v>
-      </c>
-      <c r="M25" s="15">
-        <v>94</v>
-      </c>
-      <c r="N25" s="8">
-        <v>96</v>
-      </c>
-      <c r="O25" s="10">
-        <v>110</v>
-      </c>
-      <c r="P25" s="10">
+      <c r="L25" s="10">
         <v>142</v>
       </c>
-      <c r="Q25" s="19">
+      <c r="M25" s="19">
         <v>103</v>
       </c>
-      <c r="R25" s="14">
+      <c r="N25" s="14">
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3748,50 +3436,38 @@
       <c r="D26" s="10">
         <v>111</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="19">
+        <v>103</v>
+      </c>
+      <c r="F26" s="10">
+        <v>123</v>
+      </c>
+      <c r="G26" s="10">
         <v>111</v>
       </c>
-      <c r="F26" s="19">
-        <v>103</v>
-      </c>
-      <c r="G26" s="10">
-        <v>112</v>
-      </c>
-      <c r="H26" s="13">
-        <v>104</v>
-      </c>
-      <c r="I26" s="19">
-        <v>103</v>
+      <c r="H26" s="10">
+        <v>115</v>
+      </c>
+      <c r="I26" s="10">
+        <v>116</v>
       </c>
       <c r="J26" s="10">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K26" s="10">
-        <v>111</v>
-      </c>
-      <c r="L26" s="10">
-        <v>115</v>
-      </c>
-      <c r="M26" s="10">
-        <v>116</v>
-      </c>
-      <c r="N26" s="10">
-        <v>116</v>
-      </c>
-      <c r="O26" s="10">
         <v>174</v>
       </c>
-      <c r="P26" s="4">
+      <c r="L26" s="4">
         <v>102</v>
       </c>
-      <c r="Q26" s="14">
+      <c r="M26" s="14">
         <v>105</v>
       </c>
-      <c r="R26" s="22">
+      <c r="N26" s="22">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -3804,50 +3480,38 @@
       <c r="D27" s="19">
         <v>103</v>
       </c>
-      <c r="E27" s="6">
-        <v>99</v>
-      </c>
-      <c r="F27" s="4">
-        <v>102</v>
-      </c>
-      <c r="G27" s="12">
-        <v>101</v>
-      </c>
-      <c r="H27" s="4">
-        <v>102</v>
-      </c>
-      <c r="I27" s="14">
+      <c r="E27" s="14">
         <v>105</v>
       </c>
-      <c r="J27" s="18">
+      <c r="F27" s="18">
         <v>106</v>
       </c>
-      <c r="K27" s="18">
+      <c r="G27" s="18">
         <v>106</v>
       </c>
-      <c r="L27" s="13">
+      <c r="H27" s="13">
         <v>104</v>
       </c>
-      <c r="M27" s="13">
+      <c r="I27" s="13">
         <v>104</v>
       </c>
-      <c r="N27" s="10">
+      <c r="J27" s="10">
         <v>115</v>
       </c>
-      <c r="O27" s="10">
+      <c r="K27" s="10">
         <v>156</v>
       </c>
-      <c r="P27" s="23">
+      <c r="L27" s="23">
         <v>76</v>
       </c>
-      <c r="Q27" s="29">
+      <c r="M27" s="29">
         <v>109</v>
       </c>
-      <c r="R27" s="9">
+      <c r="N27" s="9">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1</v>
       </c>
@@ -3860,50 +3524,38 @@
       <c r="D28" s="7">
         <v>97</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="6">
+        <v>99</v>
+      </c>
+      <c r="F28" s="15">
+        <v>94</v>
+      </c>
+      <c r="G28" s="7">
         <v>97</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>99</v>
       </c>
-      <c r="G28" s="3">
+      <c r="I28" s="19">
+        <v>103</v>
+      </c>
+      <c r="J28" s="9">
+        <v>88</v>
+      </c>
+      <c r="K28" s="10">
+        <v>189</v>
+      </c>
+      <c r="L28" s="9">
+        <v>84</v>
+      </c>
+      <c r="M28" s="15">
+        <v>94</v>
+      </c>
+      <c r="N28" s="3">
         <v>98</v>
       </c>
-      <c r="H28" s="5">
-        <v>100</v>
-      </c>
-      <c r="I28" s="6">
-        <v>99</v>
-      </c>
-      <c r="J28" s="15">
-        <v>94</v>
-      </c>
-      <c r="K28" s="7">
-        <v>97</v>
-      </c>
-      <c r="L28" s="6">
-        <v>99</v>
-      </c>
-      <c r="M28" s="19">
-        <v>103</v>
-      </c>
-      <c r="N28" s="9">
-        <v>88</v>
-      </c>
-      <c r="O28" s="10">
-        <v>189</v>
-      </c>
-      <c r="P28" s="9">
-        <v>84</v>
-      </c>
-      <c r="Q28" s="15">
-        <v>94</v>
-      </c>
-      <c r="R28" s="3">
-        <v>98</v>
-      </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>2</v>
       </c>
@@ -3916,50 +3568,38 @@
       <c r="D29" s="4">
         <v>102</v>
       </c>
-      <c r="E29" s="14">
-        <v>105</v>
+      <c r="E29" s="19">
+        <v>103</v>
       </c>
       <c r="F29" s="13">
         <v>104</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="4">
+        <v>102</v>
+      </c>
+      <c r="H29" s="5">
+        <v>100</v>
+      </c>
+      <c r="I29" s="6">
+        <v>99</v>
+      </c>
+      <c r="J29" s="19">
+        <v>103</v>
+      </c>
+      <c r="K29" s="9">
+        <v>85</v>
+      </c>
+      <c r="L29" s="13">
         <v>104</v>
       </c>
-      <c r="H29" s="4">
-        <v>102</v>
-      </c>
-      <c r="I29" s="19">
-        <v>103</v>
-      </c>
-      <c r="J29" s="13">
-        <v>104</v>
-      </c>
-      <c r="K29" s="4">
-        <v>102</v>
-      </c>
-      <c r="L29" s="5">
-        <v>100</v>
-      </c>
-      <c r="M29" s="6">
-        <v>99</v>
-      </c>
-      <c r="N29" s="19">
-        <v>103</v>
-      </c>
-      <c r="O29" s="9">
-        <v>85</v>
-      </c>
-      <c r="P29" s="13">
-        <v>104</v>
-      </c>
-      <c r="Q29" s="27">
+      <c r="M29" s="27">
         <v>107</v>
       </c>
-      <c r="R29" s="27">
+      <c r="N29" s="27">
         <v>107</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -3972,50 +3612,38 @@
       <c r="D30" s="6">
         <v>99</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="15">
+        <v>94</v>
+      </c>
+      <c r="F30" s="3">
         <v>98</v>
       </c>
-      <c r="F30" s="8">
-        <v>96</v>
-      </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
+        <v>100</v>
+      </c>
+      <c r="H30" s="6">
         <v>99</v>
       </c>
-      <c r="H30" s="7">
-        <v>97</v>
-      </c>
-      <c r="I30" s="15">
-        <v>94</v>
-      </c>
-      <c r="J30" s="3">
-        <v>98</v>
-      </c>
-      <c r="K30" s="5">
-        <v>100</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="I30" s="13">
+        <v>104</v>
+      </c>
+      <c r="J30" s="9">
+        <v>88</v>
+      </c>
+      <c r="K30" s="34">
+        <v>73</v>
+      </c>
+      <c r="L30" s="16">
+        <v>95</v>
+      </c>
+      <c r="M30" s="19">
+        <v>103</v>
+      </c>
+      <c r="N30" s="6">
         <v>99</v>
       </c>
-      <c r="M30" s="13">
-        <v>104</v>
-      </c>
-      <c r="N30" s="9">
-        <v>88</v>
-      </c>
-      <c r="O30" s="34">
-        <v>73</v>
-      </c>
-      <c r="P30" s="16">
-        <v>95</v>
-      </c>
-      <c r="Q30" s="19">
-        <v>103</v>
-      </c>
-      <c r="R30" s="6">
-        <v>99</v>
-      </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -4028,46 +3656,34 @@
       <c r="D31" s="6">
         <v>99</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="4">
+        <v>102</v>
+      </c>
+      <c r="F31" s="3">
         <v>98</v>
       </c>
-      <c r="F31" s="12">
-        <v>101</v>
-      </c>
-      <c r="G31" s="8">
-        <v>96</v>
-      </c>
-      <c r="H31" s="6">
-        <v>99</v>
-      </c>
-      <c r="I31" s="4">
-        <v>102</v>
-      </c>
-      <c r="J31" s="3">
+      <c r="G31" s="3">
         <v>98</v>
       </c>
-      <c r="K31" s="3">
-        <v>98</v>
-      </c>
-      <c r="L31" s="20">
+      <c r="H31" s="20">
         <v>92</v>
       </c>
-      <c r="M31" s="9">
+      <c r="I31" s="9">
         <v>87</v>
       </c>
-      <c r="N31" s="20">
+      <c r="J31" s="20">
         <v>92</v>
       </c>
-      <c r="O31" s="35">
+      <c r="K31" s="35">
         <v>44</v>
       </c>
-      <c r="P31" s="10">
+      <c r="L31" s="10">
         <v>119</v>
       </c>
-      <c r="Q31" s="29">
+      <c r="M31" s="29">
         <v>109</v>
       </c>
-      <c r="R31" s="13">
+      <c r="N31" s="13">
         <v>104</v>
       </c>
     </row>

--- a/projectionsv2/rolling_lhb_pf.xlsx
+++ b/projectionsv2/rolling_lhb_pf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dresi\Documents\Baseball Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F79E8E6-7CC1-4D23-B99A-981FC0314A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0435FC9-2C88-4559-9235-889904ECE86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{31A4AC9A-A4C1-4A2B-9B48-AA32E1DA034C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31A4AC9A-A4C1-4A2B-9B48-AA32E1DA034C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -619,7 +619,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -667,7 +667,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -715,7 +715,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -763,7 +763,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -811,7 +811,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -859,7 +859,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -907,7 +907,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -955,7 +955,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1003,7 +1003,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1051,7 +1051,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1099,7 +1099,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1147,7 +1147,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1195,7 +1195,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1243,7 +1243,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1291,7 +1291,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1339,7 +1339,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1387,7 +1387,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1435,7 +1435,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1483,7 +1483,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1531,7 +1531,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1579,7 +1579,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1627,7 +1627,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1675,7 +1675,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1723,7 +1723,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1771,7 +1771,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1819,7 +1819,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1867,7 +1867,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1915,7 +1915,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1963,7 +1963,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2378,37 +2378,37 @@
         <v>7</v>
       </c>
       <c r="D2" s="3">
+        <v>99</v>
+      </c>
+      <c r="E2" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="F2" s="8">
         <v>98</v>
       </c>
-      <c r="E2" s="7">
-        <v>97</v>
-      </c>
-      <c r="F2" s="8">
-        <v>96</v>
-      </c>
       <c r="G2" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="H2" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="I2" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J2" s="9">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K2" s="10">
-        <v>117</v>
+        <v>108.5</v>
       </c>
       <c r="L2" s="10">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="M2" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="N2" s="10">
-        <v>111</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -2422,37 +2422,37 @@
         <v>7</v>
       </c>
       <c r="D3" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="E3" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="F3" s="4">
         <v>101</v>
-      </c>
-      <c r="E3" s="12">
-        <v>101</v>
-      </c>
-      <c r="F3" s="4">
-        <v>102</v>
       </c>
       <c r="G3" s="5">
         <v>100</v>
       </c>
       <c r="H3" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="I3" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="J3" s="3">
         <v>99</v>
       </c>
-      <c r="I3" s="7">
-        <v>97</v>
-      </c>
-      <c r="J3" s="3">
-        <v>98</v>
-      </c>
       <c r="K3" s="10">
-        <v>115</v>
+        <v>107.5</v>
       </c>
       <c r="L3" s="10">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M3" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N3" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2466,37 +2466,37 @@
         <v>7</v>
       </c>
       <c r="D4" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="E4" s="17">
+        <v>96.5</v>
+      </c>
+      <c r="F4" s="15">
         <v>97</v>
       </c>
-      <c r="E4" s="17">
-        <v>93</v>
-      </c>
-      <c r="F4" s="15">
-        <v>94</v>
-      </c>
       <c r="G4" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H4" s="16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I4" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J4" s="18">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K4" s="10">
-        <v>115</v>
+        <v>107.5</v>
       </c>
       <c r="L4" s="9">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="M4" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="N4" s="16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -2510,37 +2510,37 @@
         <v>7</v>
       </c>
       <c r="D5" s="3">
+        <v>99</v>
+      </c>
+      <c r="E5" s="3">
+        <v>99</v>
+      </c>
+      <c r="F5" s="8">
         <v>98</v>
       </c>
-      <c r="E5" s="3">
-        <v>98</v>
-      </c>
-      <c r="F5" s="8">
-        <v>96</v>
-      </c>
       <c r="G5" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="H5" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="I5" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="J5" s="10">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K5" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="L5" s="16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M5" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="N5" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -2554,37 +2554,37 @@
         <v>7</v>
       </c>
       <c r="D6" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="E6" s="4">
+        <v>101</v>
+      </c>
+      <c r="F6" s="3">
         <v>99</v>
       </c>
-      <c r="E6" s="4">
+      <c r="G6" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="H6" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="I6" s="14">
+        <v>102.5</v>
+      </c>
+      <c r="J6" s="9">
+        <v>95</v>
+      </c>
+      <c r="K6" s="15">
+        <v>97</v>
+      </c>
+      <c r="L6" s="13">
         <v>102</v>
       </c>
-      <c r="F6" s="3">
-        <v>98</v>
-      </c>
-      <c r="G6" s="6">
-        <v>99</v>
-      </c>
-      <c r="H6" s="12">
-        <v>101</v>
-      </c>
-      <c r="I6" s="14">
-        <v>105</v>
-      </c>
-      <c r="J6" s="9">
-        <v>90</v>
-      </c>
-      <c r="K6" s="15">
-        <v>94</v>
-      </c>
-      <c r="L6" s="13">
-        <v>104</v>
-      </c>
       <c r="M6" s="20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N6" s="10">
-        <v>113</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2598,37 +2598,37 @@
         <v>7</v>
       </c>
       <c r="D7" s="3">
+        <v>99</v>
+      </c>
+      <c r="E7" s="3">
+        <v>99</v>
+      </c>
+      <c r="F7" s="8">
         <v>98</v>
       </c>
-      <c r="E7" s="3">
-        <v>98</v>
-      </c>
-      <c r="F7" s="8">
-        <v>96</v>
-      </c>
       <c r="G7" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="H7" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="I7" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J7" s="9">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K7" s="21">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="L7" s="10">
-        <v>119</v>
+        <v>109.5</v>
       </c>
       <c r="M7" s="21">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="N7" s="10">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2642,37 +2642,37 @@
         <v>7</v>
       </c>
       <c r="D8" s="3">
+        <v>99</v>
+      </c>
+      <c r="E8" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="F8" s="8">
         <v>98</v>
       </c>
-      <c r="E8" s="6">
-        <v>99</v>
-      </c>
-      <c r="F8" s="8">
-        <v>96</v>
-      </c>
       <c r="G8" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="H8" s="5">
         <v>100</v>
       </c>
       <c r="I8" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J8" s="5">
         <v>100</v>
       </c>
       <c r="K8" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L8" s="9">
-        <v>87</v>
+        <v>93.5</v>
       </c>
       <c r="M8" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N8" s="22">
-        <v>91</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2686,37 +2686,37 @@
         <v>7</v>
       </c>
       <c r="D9" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="E9" s="5">
         <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9" s="5">
         <v>100</v>
       </c>
       <c r="H9" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="I9" s="4">
         <v>101</v>
       </c>
-      <c r="I9" s="4">
-        <v>102</v>
-      </c>
       <c r="J9" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K9" s="10">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="L9" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M9" s="19">
+        <v>101.5</v>
+      </c>
+      <c r="N9" s="18">
         <v>103</v>
-      </c>
-      <c r="N9" s="18">
-        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -2730,37 +2730,37 @@
         <v>7</v>
       </c>
       <c r="D10" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="E10" s="3">
         <v>99</v>
       </c>
-      <c r="E10" s="3">
-        <v>98</v>
-      </c>
       <c r="F10" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G10" s="5">
         <v>100</v>
       </c>
       <c r="H10" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="I10" s="4">
         <v>101</v>
       </c>
-      <c r="I10" s="4">
-        <v>102</v>
-      </c>
       <c r="J10" s="18">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K10" s="10">
-        <v>177</v>
+        <v>138.5</v>
       </c>
       <c r="L10" s="23">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="M10" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N10" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2774,37 +2774,37 @@
         <v>7</v>
       </c>
       <c r="D11" s="3">
+        <v>99</v>
+      </c>
+      <c r="E11" s="4">
+        <v>101</v>
+      </c>
+      <c r="F11" s="8">
         <v>98</v>
       </c>
-      <c r="E11" s="4">
-        <v>102</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="G11" s="8">
+        <v>98</v>
+      </c>
+      <c r="H11" s="16">
+        <v>97.5</v>
+      </c>
+      <c r="I11" s="20">
         <v>96</v>
       </c>
-      <c r="G11" s="8">
-        <v>96</v>
-      </c>
-      <c r="H11" s="16">
-        <v>95</v>
-      </c>
-      <c r="I11" s="20">
-        <v>92</v>
-      </c>
       <c r="J11" s="16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K11" s="23">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L11" s="10">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="M11" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="N11" s="12">
-        <v>101</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2818,37 +2818,37 @@
         <v>7</v>
       </c>
       <c r="D12" s="8">
+        <v>98</v>
+      </c>
+      <c r="E12" s="14">
+        <v>102.5</v>
+      </c>
+      <c r="F12" s="20">
         <v>96</v>
       </c>
-      <c r="E12" s="14">
-        <v>105</v>
-      </c>
-      <c r="F12" s="20">
-        <v>92</v>
-      </c>
       <c r="G12" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="H12" s="5">
         <v>100</v>
       </c>
       <c r="I12" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J12" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K12" s="10">
-        <v>113</v>
+        <v>106.5</v>
       </c>
       <c r="L12" s="24">
-        <v>77</v>
+        <v>88.5</v>
       </c>
       <c r="M12" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N12" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2862,37 +2862,37 @@
         <v>7</v>
       </c>
       <c r="D13" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>98</v>
+      </c>
+      <c r="F13" s="3">
         <v>99</v>
-      </c>
-      <c r="E13" s="8">
-        <v>96</v>
-      </c>
-      <c r="F13" s="3">
-        <v>98</v>
       </c>
       <c r="G13" s="5">
         <v>100</v>
       </c>
       <c r="H13" s="4">
+        <v>101</v>
+      </c>
+      <c r="I13" s="13">
         <v>102</v>
       </c>
-      <c r="I13" s="13">
-        <v>104</v>
-      </c>
       <c r="J13" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="K13" s="25">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="L13" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M13" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="N13" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2906,37 +2906,37 @@
         <v>7</v>
       </c>
       <c r="D14" s="22">
-        <v>91</v>
+        <v>95.5</v>
       </c>
       <c r="E14" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="F14" s="9">
+        <v>91.5</v>
+      </c>
+      <c r="G14" s="22">
+        <v>95.5</v>
+      </c>
+      <c r="H14" s="22">
+        <v>95.5</v>
+      </c>
+      <c r="I14" s="15">
         <v>97</v>
       </c>
-      <c r="F14" s="9">
-        <v>83</v>
-      </c>
-      <c r="G14" s="22">
-        <v>91</v>
-      </c>
-      <c r="H14" s="22">
-        <v>91</v>
-      </c>
-      <c r="I14" s="15">
-        <v>94</v>
-      </c>
       <c r="J14" s="9">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K14" s="26">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L14" s="20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M14" s="20">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N14" s="10">
-        <v>115</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2950,37 +2950,37 @@
         <v>7</v>
       </c>
       <c r="D15" s="13">
+        <v>102</v>
+      </c>
+      <c r="E15" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="F15" s="21">
         <v>104</v>
       </c>
-      <c r="E15" s="7">
-        <v>97</v>
-      </c>
-      <c r="F15" s="21">
-        <v>108</v>
-      </c>
       <c r="G15" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H15" s="27">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="I15" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="J15" s="10">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="K15" s="10">
-        <v>129</v>
+        <v>114.5</v>
       </c>
       <c r="L15" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M15" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N15" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -2994,37 +2994,37 @@
         <v>7</v>
       </c>
       <c r="D16" s="8">
+        <v>98</v>
+      </c>
+      <c r="E16" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="F16" s="20">
         <v>96</v>
       </c>
-      <c r="E16" s="7">
+      <c r="G16" s="3">
+        <v>99</v>
+      </c>
+      <c r="H16" s="22">
+        <v>95.5</v>
+      </c>
+      <c r="I16" s="15">
         <v>97</v>
       </c>
-      <c r="F16" s="20">
-        <v>92</v>
-      </c>
-      <c r="G16" s="3">
-        <v>98</v>
-      </c>
-      <c r="H16" s="22">
-        <v>91</v>
-      </c>
-      <c r="I16" s="15">
-        <v>94</v>
-      </c>
       <c r="J16" s="9">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K16" s="28">
-        <v>65</v>
+        <v>82.5</v>
       </c>
       <c r="L16" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="M16" s="29">
-        <v>109</v>
+        <v>104.5</v>
       </c>
       <c r="N16" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -3038,37 +3038,37 @@
         <v>7</v>
       </c>
       <c r="D17" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E17" s="5">
         <v>100</v>
       </c>
       <c r="F17" s="21">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G17" s="13">
+        <v>102</v>
+      </c>
+      <c r="H17" s="21">
         <v>104</v>
       </c>
-      <c r="H17" s="21">
-        <v>108</v>
-      </c>
       <c r="I17" s="10">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="J17" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="K17" s="30">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L17" s="5">
         <v>100</v>
       </c>
       <c r="M17" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N17" s="9">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -3085,34 +3085,34 @@
         <v>100</v>
       </c>
       <c r="E18" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="5">
         <v>100</v>
       </c>
       <c r="G18" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="H18" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="I18" s="27">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="J18" s="9">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K18" s="24">
-        <v>77</v>
+        <v>88.5</v>
       </c>
       <c r="L18" s="10">
-        <v>111</v>
+        <v>105.5</v>
       </c>
       <c r="M18" s="22">
-        <v>91</v>
+        <v>95.5</v>
       </c>
       <c r="N18" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -3126,34 +3126,34 @@
         <v>7</v>
       </c>
       <c r="D19" s="8">
+        <v>98</v>
+      </c>
+      <c r="E19" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="F19" s="20">
         <v>96</v>
       </c>
-      <c r="E19" s="12">
-        <v>101</v>
-      </c>
-      <c r="F19" s="20">
-        <v>92</v>
-      </c>
       <c r="G19" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="H19" s="15">
         <v>97</v>
       </c>
-      <c r="H19" s="15">
-        <v>94</v>
-      </c>
       <c r="I19" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J19" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="K19" s="31">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="L19" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="M19" s="12">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="N19" s="5">
         <v>100</v>
@@ -3170,37 +3170,37 @@
         <v>7</v>
       </c>
       <c r="D20" s="19">
+        <v>101.5</v>
+      </c>
+      <c r="E20" s="4">
+        <v>101</v>
+      </c>
+      <c r="F20" s="18">
         <v>103</v>
       </c>
-      <c r="E20" s="4">
-        <v>102</v>
-      </c>
-      <c r="F20" s="18">
-        <v>106</v>
-      </c>
       <c r="G20" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="H20" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="I20" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="J20" s="20">
+        <v>96</v>
+      </c>
+      <c r="K20" s="10">
+        <v>112.5</v>
+      </c>
+      <c r="L20" s="10">
+        <v>113.5</v>
+      </c>
+      <c r="M20" s="4">
         <v>101</v>
       </c>
-      <c r="H20" s="12">
+      <c r="N20" s="4">
         <v>101</v>
-      </c>
-      <c r="I20" s="7">
-        <v>97</v>
-      </c>
-      <c r="J20" s="20">
-        <v>92</v>
-      </c>
-      <c r="K20" s="10">
-        <v>125</v>
-      </c>
-      <c r="L20" s="10">
-        <v>127</v>
-      </c>
-      <c r="M20" s="4">
-        <v>102</v>
-      </c>
-      <c r="N20" s="4">
-        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -3214,37 +3214,37 @@
         <v>7</v>
       </c>
       <c r="D21" s="13">
+        <v>102</v>
+      </c>
+      <c r="E21" s="13">
+        <v>102</v>
+      </c>
+      <c r="F21" s="21">
         <v>104</v>
       </c>
-      <c r="E21" s="13">
-        <v>104</v>
-      </c>
-      <c r="F21" s="21">
-        <v>108</v>
-      </c>
       <c r="G21" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="H21" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I21" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="J21" s="10">
-        <v>113</v>
+        <v>106.5</v>
       </c>
       <c r="K21" s="32">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="L21" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M21" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="N21" s="17">
-        <v>93</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -3258,37 +3258,37 @@
         <v>7</v>
       </c>
       <c r="D22" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="E22" s="14">
+        <v>102.5</v>
+      </c>
+      <c r="F22" s="4">
         <v>101</v>
-      </c>
-      <c r="E22" s="14">
-        <v>105</v>
-      </c>
-      <c r="F22" s="4">
-        <v>102</v>
       </c>
       <c r="G22" s="5">
         <v>100</v>
       </c>
       <c r="H22" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I22" s="5">
         <v>100</v>
       </c>
       <c r="J22" s="12">
+        <v>100.5</v>
+      </c>
+      <c r="K22" s="33">
+        <v>83.5</v>
+      </c>
+      <c r="L22" s="10">
+        <v>106.5</v>
+      </c>
+      <c r="M22" s="4">
         <v>101</v>
       </c>
-      <c r="K22" s="33">
-        <v>67</v>
-      </c>
-      <c r="L22" s="10">
-        <v>113</v>
-      </c>
-      <c r="M22" s="4">
-        <v>102</v>
-      </c>
       <c r="N22" s="7">
-        <v>97</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -3302,37 +3302,37 @@
         <v>7</v>
       </c>
       <c r="D23" s="15">
+        <v>97</v>
+      </c>
+      <c r="E23" s="8">
+        <v>98</v>
+      </c>
+      <c r="F23" s="9">
         <v>94</v>
       </c>
-      <c r="E23" s="8">
-        <v>96</v>
-      </c>
-      <c r="F23" s="9">
-        <v>88</v>
-      </c>
       <c r="G23" s="15">
+        <v>97</v>
+      </c>
+      <c r="H23" s="15">
+        <v>97</v>
+      </c>
+      <c r="I23" s="15">
+        <v>97</v>
+      </c>
+      <c r="J23" s="8">
+        <v>98</v>
+      </c>
+      <c r="K23" s="19">
+        <v>101.5</v>
+      </c>
+      <c r="L23" s="9">
         <v>94</v>
       </c>
-      <c r="H23" s="15">
-        <v>94</v>
-      </c>
-      <c r="I23" s="15">
-        <v>94</v>
-      </c>
-      <c r="J23" s="8">
-        <v>96</v>
-      </c>
-      <c r="K23" s="19">
-        <v>103</v>
-      </c>
-      <c r="L23" s="9">
-        <v>88</v>
-      </c>
       <c r="M23" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N23" s="10">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -3346,37 +3346,37 @@
         <v>7</v>
       </c>
       <c r="D24" s="10">
+        <v>105</v>
+      </c>
+      <c r="E24" s="13">
+        <v>102</v>
+      </c>
+      <c r="F24" s="10">
+        <v>110.5</v>
+      </c>
+      <c r="G24" s="29">
+        <v>104.5</v>
+      </c>
+      <c r="H24" s="10">
+        <v>106.5</v>
+      </c>
+      <c r="I24" s="27">
+        <v>103.5</v>
+      </c>
+      <c r="J24" s="10">
+        <v>121</v>
+      </c>
+      <c r="K24" s="10">
         <v>110</v>
       </c>
-      <c r="E24" s="13">
-        <v>104</v>
-      </c>
-      <c r="F24" s="10">
-        <v>121</v>
-      </c>
-      <c r="G24" s="29">
-        <v>109</v>
-      </c>
-      <c r="H24" s="10">
-        <v>113</v>
-      </c>
-      <c r="I24" s="27">
-        <v>107</v>
-      </c>
-      <c r="J24" s="10">
-        <v>142</v>
-      </c>
-      <c r="K24" s="10">
-        <v>120</v>
-      </c>
       <c r="L24" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M24" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="N24" s="9">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -3390,37 +3390,37 @@
         <v>7</v>
       </c>
       <c r="D25" s="14">
+        <v>102.5</v>
+      </c>
+      <c r="E25" s="15">
+        <v>97</v>
+      </c>
+      <c r="F25" s="10">
         <v>105</v>
       </c>
-      <c r="E25" s="15">
-        <v>94</v>
-      </c>
-      <c r="F25" s="10">
-        <v>110</v>
-      </c>
       <c r="G25" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H25" s="12">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="I25" s="15">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J25" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K25" s="10">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L25" s="10">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="M25" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="N25" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -3434,37 +3434,37 @@
         <v>7</v>
       </c>
       <c r="D26" s="10">
-        <v>111</v>
+        <v>105.5</v>
       </c>
       <c r="E26" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="F26" s="10">
-        <v>123</v>
+        <v>111.5</v>
       </c>
       <c r="G26" s="10">
-        <v>111</v>
+        <v>105.5</v>
       </c>
       <c r="H26" s="10">
-        <v>115</v>
+        <v>107.5</v>
       </c>
       <c r="I26" s="10">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J26" s="10">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="K26" s="10">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="L26" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M26" s="14">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="N26" s="22">
-        <v>91</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -3478,37 +3478,37 @@
         <v>7</v>
       </c>
       <c r="D27" s="19">
+        <v>101.5</v>
+      </c>
+      <c r="E27" s="14">
+        <v>102.5</v>
+      </c>
+      <c r="F27" s="18">
         <v>103</v>
       </c>
-      <c r="E27" s="14">
-        <v>105</v>
-      </c>
-      <c r="F27" s="18">
-        <v>106</v>
-      </c>
       <c r="G27" s="18">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H27" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I27" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J27" s="10">
-        <v>115</v>
+        <v>107.5</v>
       </c>
       <c r="K27" s="10">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="L27" s="23">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="M27" s="29">
-        <v>109</v>
+        <v>104.5</v>
       </c>
       <c r="N27" s="9">
-        <v>87</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -3522,37 +3522,37 @@
         <v>7</v>
       </c>
       <c r="D28" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="E28" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="F28" s="15">
         <v>97</v>
       </c>
-      <c r="E28" s="6">
+      <c r="G28" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="H28" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="I28" s="19">
+        <v>101.5</v>
+      </c>
+      <c r="J28" s="9">
+        <v>94</v>
+      </c>
+      <c r="K28" s="10">
+        <v>144.5</v>
+      </c>
+      <c r="L28" s="9">
+        <v>92</v>
+      </c>
+      <c r="M28" s="15">
+        <v>97</v>
+      </c>
+      <c r="N28" s="3">
         <v>99</v>
-      </c>
-      <c r="F28" s="15">
-        <v>94</v>
-      </c>
-      <c r="G28" s="7">
-        <v>97</v>
-      </c>
-      <c r="H28" s="6">
-        <v>99</v>
-      </c>
-      <c r="I28" s="19">
-        <v>103</v>
-      </c>
-      <c r="J28" s="9">
-        <v>88</v>
-      </c>
-      <c r="K28" s="10">
-        <v>189</v>
-      </c>
-      <c r="L28" s="9">
-        <v>84</v>
-      </c>
-      <c r="M28" s="15">
-        <v>94</v>
-      </c>
-      <c r="N28" s="3">
-        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -3566,37 +3566,37 @@
         <v>7</v>
       </c>
       <c r="D29" s="4">
+        <v>101</v>
+      </c>
+      <c r="E29" s="19">
+        <v>101.5</v>
+      </c>
+      <c r="F29" s="13">
         <v>102</v>
       </c>
-      <c r="E29" s="19">
-        <v>103</v>
-      </c>
-      <c r="F29" s="13">
-        <v>104</v>
-      </c>
       <c r="G29" s="4">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H29" s="5">
         <v>100</v>
       </c>
       <c r="I29" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="J29" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="K29" s="9">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L29" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M29" s="27">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="N29" s="27">
-        <v>107</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -3610,37 +3610,37 @@
         <v>7</v>
       </c>
       <c r="D30" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="E30" s="15">
+        <v>97</v>
+      </c>
+      <c r="F30" s="3">
         <v>99</v>
-      </c>
-      <c r="E30" s="15">
-        <v>94</v>
-      </c>
-      <c r="F30" s="3">
-        <v>98</v>
       </c>
       <c r="G30" s="5">
         <v>100</v>
       </c>
       <c r="H30" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="I30" s="13">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J30" s="9">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K30" s="34">
-        <v>73</v>
+        <v>86.5</v>
       </c>
       <c r="L30" s="16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M30" s="19">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="N30" s="6">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -3654,37 +3654,37 @@
         <v>7</v>
       </c>
       <c r="D31" s="6">
+        <v>99.5</v>
+      </c>
+      <c r="E31" s="4">
+        <v>101</v>
+      </c>
+      <c r="F31" s="3">
         <v>99</v>
       </c>
-      <c r="E31" s="4">
+      <c r="G31" s="3">
+        <v>99</v>
+      </c>
+      <c r="H31" s="20">
+        <v>96</v>
+      </c>
+      <c r="I31" s="9">
+        <v>93.5</v>
+      </c>
+      <c r="J31" s="20">
+        <v>96</v>
+      </c>
+      <c r="K31" s="35">
+        <v>72</v>
+      </c>
+      <c r="L31" s="10">
+        <v>109.5</v>
+      </c>
+      <c r="M31" s="29">
+        <v>104.5</v>
+      </c>
+      <c r="N31" s="13">
         <v>102</v>
-      </c>
-      <c r="F31" s="3">
-        <v>98</v>
-      </c>
-      <c r="G31" s="3">
-        <v>98</v>
-      </c>
-      <c r="H31" s="20">
-        <v>92</v>
-      </c>
-      <c r="I31" s="9">
-        <v>87</v>
-      </c>
-      <c r="J31" s="20">
-        <v>92</v>
-      </c>
-      <c r="K31" s="35">
-        <v>44</v>
-      </c>
-      <c r="L31" s="10">
-        <v>119</v>
-      </c>
-      <c r="M31" s="29">
-        <v>109</v>
-      </c>
-      <c r="N31" s="13">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
